--- a/example_data.xlsx
+++ b/example_data.xlsx
@@ -18,6 +18,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VLAN_500_Guest-Wifi" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VLAN_600_Colo-Hosting" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VLAN_700_Backup-Net" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VLAN_800_Public-Web" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VLAN_810_Cust-Widgets" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VLAN_999_Transit" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Owned_Subnets" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -6075,6 +6079,1844 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>VLAN Metadata</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>VLAN 800</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Name: Public-Web</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Routed: Yes</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Uplink: FW-Ext Gi0/1</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Customer: Acme Corp</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Location: DC-East-1</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Comment: Public-facing services (NAT + direct)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Subnet Name</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>CIDR</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>IP Address</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Customer</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Comment</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Asset</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Interface</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>Network Connection</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Web-Public</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>203.0.113.0/27</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>203.0.113.1</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Acme Corp</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>DC-East-1</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Gateway</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Palo Alto PA-5260</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Gi0/1</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Direct to Firewall</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Web-Public</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>203.0.113.0/27</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>203.0.113.2</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Acme Corp</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>DC-East-1</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>nginx-prod-01</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dell R740</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>eth0</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>LACP to TOR-A</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Web-Public</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>203.0.113.0/27</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>203.0.113.3</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Acme Corp</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>DC-East-1</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>nginx-prod-02</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Dell R740</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>eth0</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>LACP to TOR-A</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Web-Public</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>203.0.113.0/27</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>203.0.113.4</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Acme Corp</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>DC-East-1</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>nginx-prod-03</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Dell R740</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>eth0</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>LACP to TOR-B</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Web-Public</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>203.0.113.0/27</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>203.0.113.5</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Acme Corp</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>DC-East-1</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>HAProxy VIP - primary</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>F5 BIG-IP i5800</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>bond0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Web-Public</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>203.0.113.0/27</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>203.0.113.6</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Acme Corp</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>DC-East-1</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>HAProxy VIP - standby</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>F5 BIG-IP i5800</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>bond0</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Web-Public</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>203.0.113.0/27</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>203.0.113.7</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Globex Industries</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>DC-East-1</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Customer portal</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Ubuntu 22.04 LTS</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>ens192</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Web-Public</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>203.0.113.0/27</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>203.0.113.8</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Acme Corp</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>DC-East-1</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>API gateway</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>K8s Worker Node</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>eth0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Web-Public</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>203.0.113.0/27</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>203.0.113.9</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Acme Corp</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>DC-East-1</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Webhook receiver</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Docker Host</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>eth0</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Web-Public</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>203.0.113.0/27</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>203.0.113.10</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Acme Corp</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>DC-East-1</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Status page (Cachet)</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Ubuntu 22.04 LTS</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>ens192</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Web-Public</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>203.0.113.0/27</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>203.0.113.11</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Oscorp Data</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>DC-East-1</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Customer API endpoint</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>RHEL 9 Server</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>bond0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Web-Public</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>203.0.113.0/27</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>203.0.113.12</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Acme Corp</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>DC-East-1</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Scheduled for decom Q3</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Cisco C220 M5</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>eth0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Web-Public</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>203.0.113.0/27</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>203.0.113.15</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Acme Corp</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>DC-East-1</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>mail relay outbound</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Ubuntu 22.04 LTS</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>ens192</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Web-Public</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>203.0.113.0/27</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>203.0.113.20</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Acme Corp</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Monitoring probe</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Raspberry Pi 4</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>eth0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Mail-Public</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>203.0.113.32/29</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>203.0.113.33</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Acme Corp</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>DC-East-1</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Gateway</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Gi0/2</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Mail-Public</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>203.0.113.32/29</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>203.0.113.34</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Acme Corp</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>DC-East-1</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>MX primary</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>HP DL360 Gen10</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>eth0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Mail-Public</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>203.0.113.32/29</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>203.0.113.35</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Acme Corp</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>DC-East-1</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>MX secondary</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>HP DL360 Gen10</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>eth0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Mail-Public</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>203.0.113.32/29</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>203.0.113.36</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Acme Corp</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>DC-East-1</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>SMTP relay</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Ubuntu 22.04 LTS</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>ens192</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Mail-Public</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>203.0.113.32/29</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>203.0.113.37</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Acme Corp</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>DC-East-1</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>SPF/DKIM signer</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Ubuntu 22.04 LTS</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>ens192</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Mail-Public</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>203.0.113.32/29</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>203.0.113.38</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Acme Corp</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>DC-East-1</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Spam filter</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Cisco C220 M5</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>eth0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>VPN-Endpoints</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>203.0.113.64/28</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>203.0.113.65</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Acme Corp</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>DC-East-1</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Gateway</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Gi0/3</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>VPN-Endpoints</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>203.0.113.64/28</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>203.0.113.66</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Acme Corp</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>DC-East-1</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>IPSec concentrator</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Palo Alto PA-5260</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>eth1</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Internet edge</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>VPN-Endpoints</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>203.0.113.64/28</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>203.0.113.67</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Acme Corp</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>DC-East-1</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>WireGuard endpoint</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Ubuntu 22.04 LTS</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>wg0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>VPN-Endpoints</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>203.0.113.64/28</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>203.0.113.70</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Acme Corp</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>DC-East-1</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Site-to-site - Chicago</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>MPLS PE link</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>VPN-Endpoints</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>203.0.113.64/28</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>203.0.113.71</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Acme Corp</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>DC-East-1</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Site-to-site - Denver</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>MPLS PE link</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>VLAN Metadata</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>VLAN 810</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Name: Cust-Widgets</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Routed: Yes</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Uplink: FW-Ext Gi0/3</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Customer: Widgets Inc</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Location: DC-East-1 Cage 7</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Comment: Dedicated customer allocation</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Subnet Name</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>CIDR</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>IP Address</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Customer</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Comment</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Asset</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Interface</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>Network Connection</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Widgets-Servers</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>203.0.113.128/26</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>203.0.113.129</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Widgets Inc</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>DC-East-1 Cage 7</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Gateway</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Gi0/0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Widgets-Servers</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>203.0.113.128/26</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>203.0.113.130</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Widgets Inc</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>DC-East-1 Cage 7</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Customer web server</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dell R640</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>eth0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Widgets-Servers</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>203.0.113.128/26</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>203.0.113.131</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Widgets Inc</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>DC-East-1 Cage 7</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Customer API</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Dell R640</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>eth0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Widgets-Servers</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>203.0.113.128/26</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>203.0.113.132</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Widgets Inc</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>DC-East-1 Cage 7</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Customer DB</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Dell R740</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>eth0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Widgets-Servers</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>203.0.113.128/26</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>203.0.113.135</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Widgets Inc</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>DC-East-1 Cage 7</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Monitoring</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Raspberry Pi 4</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>eth0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>VLAN Metadata</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>VLAN 999</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Name: Transit</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Routed: Yes</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Uplink: </t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Customer: </t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Location: DC-East-1 MDF</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Comment: Upstream transit point-to-point links</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Subnet Name</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>CIDR</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>IP Address</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Customer</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Comment</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Asset</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Interface</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>Network Connection</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Cogent-Uplink</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>198.51.100.0/30</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>198.51.100.1</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Soylent ISP</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>DC-East-1 MDF</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Our side - Cogent</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Cisco ASR 9001</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Gi0/0/0</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Cross-connect to Meet-Me</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Cogent-Uplink</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>198.51.100.0/30</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>198.51.100.2</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Soylent ISP</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>DC-East-1 MDF</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Cogent PE router</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>et-0/0/1</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Lumen-Uplink</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>198.51.100.4/30</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>198.51.100.5</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Soylent ISP</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>DC-East-1 MDF</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Our side - Lumen</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Cisco ASR 9001</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Gi0/0/1</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Cross-connect to Meet-Me</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Lumen-Uplink</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>198.51.100.4/30</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>198.51.100.6</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Soylent ISP</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>DC-East-1 MDF</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Lumen PE router</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>CIDR</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Label</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>203.0.113.0/24</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Cogent Allocation - Jan 2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>198.51.100.0/28</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Transit Block - Soylent ISP</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>192.0.2.0/24</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ARIN Transfer - Dec 2024 (staging)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>198.18.128.0/25</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Customer Block - Reserved for Initech</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/example_data.xlsx
+++ b/example_data.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I88"/>
+  <dimension ref="A1:I94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3278,6 +3278,218 @@
       <c r="F88" t="inlineStr">
         <is>
           <t>Load balancer VIP</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Mgmt-v6</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>2001:db8:10:1::/64</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Mgmt-v6</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>2001:db8:10:1::/64</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>2001:db8:10:1::1</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Acme Corp</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>HQ-MDF</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Gateway</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Cisco Nexus 9300</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Vlan10</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Mgmt-v6</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>2001:db8:10:1::/64</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>2001:db8:10:1::2</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Acme Corp</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>HQ-MDF</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Core-SW1 loopback</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Cisco Nexus 9300</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>lo0</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Mgmt-v6</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>2001:db8:10:1::/64</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>2001:db8:10:1::3</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Acme Corp</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>HQ-MDF</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Core-SW2 loopback</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Cisco Nexus 9300</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>lo0</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Mgmt-v6</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>2001:db8:10:1::/64</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>2001:db8:10:1::a</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>HQ-IDF-A</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>IDF-A switch mgmt</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Arista 7050X</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Management1</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Mgmt-v6</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>2001:db8:10:1::/64</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>2001:db8:10:1::b</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>HQ-IDF-B</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>IDF-B switch mgmt</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Arista 7050X</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Management1</t>
         </is>
       </c>
     </row>
@@ -6085,7 +6297,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:I33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -7235,6 +7447,201 @@
       <c r="I28" t="inlineStr">
         <is>
           <t>MPLS PE link</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Web-Public-v6</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2001:db8:800::/48</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Web-Public-v6</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2001:db8:800::/48</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>2001:db8:800::1</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Acme Corp</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>DC-East-1</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Gateway</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Palo Alto PA-5260</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Gi0/1</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Direct to Firewall</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Web-Public-v6</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2001:db8:800::/48</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>2001:db8:800::10</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Acme Corp</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>DC-East-1</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>nginx-prod-01 public v6</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Dell R740</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>eth0</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>LACP to TOR-A</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Web-Public-v6</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2001:db8:800::/48</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>2001:db8:800::11</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Acme Corp</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>DC-East-1</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>nginx-prod-02 public v6</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Dell R740</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>eth0</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>LACP to TOR-A</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Web-Public-v6</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2001:db8:800::/48</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>2001:db8:800::443</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Acme Corp</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>DC-East-1</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>HTTPS VIP v6</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>F5 BIG-IP i5800</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>vlan800</t>
         </is>
       </c>
     </row>
@@ -7568,7 +7975,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -7834,6 +8241,193 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Cogent-Uplink-v6</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2001:db8:999:1::/126</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Cogent-Uplink-v6</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2001:db8:999:1::/126</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2001:db8:999:1::1</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Soylent ISP</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>DC-East-1 MDF</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Our side - Cogent v6</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Cisco ASR 9001</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Gi0/0/0</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Cross-connect to Meet-Me</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Cogent-Uplink-v6</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2001:db8:999:1::/126</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2001:db8:999:1::2</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Soylent ISP</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>DC-East-1 MDF</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Cogent PE router v6</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>et-0/0/1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Lumen-Uplink-v6</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2001:db8:999:2::/126</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Lumen-Uplink-v6</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2001:db8:999:2::/126</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2001:db8:999:2::1</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Soylent ISP</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>DC-East-1 MDF</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Our side - Lumen v6</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Cisco ASR 9001</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Gi0/0/1</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Cross-connect to Meet-Me</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Lumen-Uplink-v6</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2001:db8:999:2::/126</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2001:db8:999:2::2</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Soylent ISP</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>DC-East-1 MDF</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Lumen PE router v6</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7845,7 +8439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -7909,6 +8503,30 @@
       <c r="B5" t="inlineStr">
         <is>
           <t>Customer Block - Reserved for Initech</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2001:db8:800::/48</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ARIN v6 Allocation - Mar 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2001:db8:999::/48</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Transit v6 Block - Soylent ISP</t>
         </is>
       </c>
     </row>
@@ -7923,7 +8541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I103"/>
+  <dimension ref="A1:I110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -11518,6 +12136,290 @@
       <c r="H103" t="inlineStr">
         <is>
           <t>ens192</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Web-Frontend-v6</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>2001:db8:100:1::/64</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Web-Frontend-v6</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>2001:db8:100:1::/64</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>2001:db8:100:1::1</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Acme Corp</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>DC-East-1</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Gateway</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Palo Alto PA-5260</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>ae1.100</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>Direct to Firewall</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Web-Frontend-v6</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>2001:db8:100:1::/64</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>2001:db8:100:1::10</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Acme Corp</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>DC-East-1</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>nginx-prod-01 v6</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Dell R740</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>eth0</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>LACP to TOR-A</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Web-Frontend-v6</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>2001:db8:100:1::/64</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>2001:db8:100:1::11</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Acme Corp</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>DC-East-1</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>nginx-prod-02 v6</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Dell R740</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>eth0</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>LACP to TOR-A</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Web-Frontend-v6</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>2001:db8:100:1::/64</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>2001:db8:100:1::12</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Acme Corp</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>DC-East-1</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>nginx-prod-03 v6</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Dell R740</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>eth0</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>LACP to TOR-B</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Web-Frontend-v6</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>2001:db8:100:1::/64</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>2001:db8:100:1::20</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Weyland-Yutani</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>DC-East-1</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>HAProxy v6 VIP</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>F5 BIG-IP i5800</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>vlan100</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Web-Frontend-v6</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>2001:db8:100:1::/64</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>2001:db8:100:1::cafe</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Acme Corp</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>DC-East-1</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Monitoring endpoint</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Proxmox Node</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>vlan100</t>
         </is>
       </c>
     </row>
@@ -21338,7 +22240,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I32"/>
+  <dimension ref="A1:I37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -22441,6 +23343,186 @@
       <c r="F32" t="inlineStr">
         <is>
           <t>Migrating to new VLAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>DMZ-Web-v6</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2001:db8:300:1::/64</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>DMZ-Web-v6</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2001:db8:300:1::/64</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>2001:db8:300:1::1</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Globex Industries</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>DC-West-1</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Gateway</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Palo Alto PA-5260</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>ae0.300</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>DMZ-Web-v6</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2001:db8:300:1::/64</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>2001:db8:300:1::80</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Globex Industries</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>DC-West-1</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Public web v6</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Dell R740</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>eth0</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>DMZ-Web-v6</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2001:db8:300:1::/64</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>2001:db8:300:1::81</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Globex Industries</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>DC-West-1</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Public API v6</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Dell R740</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>eth0</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>DMZ-Web-v6</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2001:db8:300:1::/64</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>2001:db8:300:1::443</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Globex Industries</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>DC-West-1</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>TLS terminator v6</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>F5 BIG-IP i5800</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>vlan300</t>
         </is>
       </c>
     </row>
